--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488267_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488267_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9341</v>
+        <v>4.2393</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4366</v>
+        <v>0.7419</v>
       </c>
       <c r="F2" t="n">
         <v>3.4975</v>
@@ -610,10 +610,10 @@
         <v>1.8529</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3159</v>
+        <v>0.6211</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0373</v>
+        <v>0.268</v>
       </c>
       <c r="U2" t="n">
         <v>0.3531</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8674</v>
+        <v>3.5168</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2968</v>
+        <v>0.7</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5706</v>
+        <v>2.8168</v>
       </c>
       <c r="G3" t="n">
         <v>1.5266</v>
@@ -688,13 +688,13 @@
         <v>1.8529</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1977</v>
+        <v>0.4517</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2226</v>
+        <v>0.1806</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0249</v>
+        <v>0.2711</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3144</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7588</v>
+        <v>2.918</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5076</v>
+        <v>2.5191</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2511</v>
+        <v>0.3988</v>
       </c>
       <c r="G4" t="n">
         <v>1.8345</v>
@@ -766,13 +766,13 @@
         <v>1.4823</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5581</v>
+        <v>-0.3989</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6056</v>
+        <v>-0.5941</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0475</v>
+        <v>0.1952</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8436</v>
+        <v>0.744</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3953</v>
+        <v>-0.1994</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2389</v>
+        <v>0.9434</v>
       </c>
       <c r="G6" t="n">
         <v>0.0135</v>
@@ -922,13 +922,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2743</v>
+        <v>0.1747</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4924</v>
+        <v>-0.2966</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7668</v>
+        <v>0.4713</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0694</v>
+        <v>-0.0387</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5131</v>
+        <v>-0.5563</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4437</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>-1.6855</v>
@@ -1078,13 +1078,13 @@
         <v>1.1117</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5044</v>
+        <v>0.535</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.092</v>
+        <v>-0.1352</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5964</v>
+        <v>0.6703</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8115</v>
+        <v>-1.1375</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0056</v>
+        <v>-1.2332</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1941</v>
+        <v>0.0956</v>
       </c>
       <c r="G9" t="n">
         <v>-2.8657</v>
@@ -1156,13 +1156,13 @@
         <v>1.297</v>
       </c>
       <c r="S9" t="n">
-        <v>1.0548</v>
+        <v>0.7287</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2873</v>
+        <v>0.0597</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7675</v>
+        <v>0.669</v>
       </c>
       <c r="V9" t="n">
         <v>0.6289</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ AMESTOY</t>
+          <t>A. GONZALEZ PALOMO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7395</v>
+        <v>-2.4707</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.2181</v>
+        <v>-3.3064</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4786</v>
+        <v>0.8357</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.7793</v>
+        <v>-1.9754</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.7978</v>
+        <v>1.4885</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0185</v>
+        <v>-3.4639</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.5485</v>
+        <v>-1.4392</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.9371</v>
+        <v>1.1722</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-2.6114</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7692</v>
+        <v>-0.5361</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1393</v>
+        <v>0.3163</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6299</v>
+        <v>-0.8524</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1853</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1117</v>
+        <v>1.4823</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1134</v>
+        <v>0.1896</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1131</v>
+        <v>-0.0143</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2266</v>
+        <v>0.2039</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2589</v>
+        <v>-0.3144</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6289</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ TORRERO</t>
+          <t>A. FERNANDEZ AMESTOY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0295</v>
+        <v>-2.9107</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.0221</v>
+        <v>-4.4139</v>
       </c>
       <c r="F11" t="n">
-        <v>1.9926</v>
+        <v>1.5032</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.1586</v>
+        <v>-1.7793</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.7993</v>
+        <v>-1.7978</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3593</v>
+        <v>0.0185</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.9641</v>
+        <v>-2.5485</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.0885</v>
+        <v>-1.9371</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1244</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.1945</v>
+        <v>0.7692</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7108</v>
+        <v>0.1393</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4837</v>
+        <v>0.6299</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.7411</v>
+        <v>0.1853</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.7793</v>
+        <v>-0.9264</v>
       </c>
       <c r="R11" t="n">
-        <v>2.0382</v>
+        <v>1.1117</v>
       </c>
       <c r="S11" t="n">
-        <v>1.8703</v>
+        <v>-0.0578</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7213000000000001</v>
+        <v>-0.309</v>
       </c>
       <c r="U11" t="n">
-        <v>1.149</v>
+        <v>0.2512</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.63</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. GONZALEZ PALOMO</t>
+          <t>H. ANDRADE CORREIA E SILVA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3592</v>
+        <v>-3.0479</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.9487</v>
+        <v>-2.9448</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5894</v>
+        <v>-0.1031</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.9754</v>
+        <v>-2.0983</v>
       </c>
       <c r="H12" t="n">
-        <v>1.4885</v>
+        <v>-1.9998</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.4639</v>
+        <v>-0.0985</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.4392</v>
+        <v>0.3551</v>
       </c>
       <c r="K12" t="n">
-        <v>1.1722</v>
+        <v>-0.8595</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.6114</v>
+        <v>1.2146</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.5361</v>
+        <v>-2.4534</v>
       </c>
       <c r="N12" t="n">
-        <v>0.3163</v>
+        <v>-1.1403</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8524</v>
+        <v>-1.3131</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.3706</v>
+        <v>-1.297</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.8529</v>
+        <v>-2.7793</v>
       </c>
       <c r="R12" t="n">
         <v>1.4823</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6989</v>
+        <v>0.033</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6566</v>
+        <v>-0.835</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0423</v>
+        <v>0.868</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3144</v>
+        <v>0.3144</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>H. ANDRADE CORREIA E SILVA</t>
+          <t>A. RODRIGUEZ TORRERO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.7641</v>
+        <v>-3.5623</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.5871</v>
+        <v>-5.555</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.177</v>
+        <v>1.9926</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.0983</v>
+        <v>-4.1586</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.9998</v>
+        <v>-3.7993</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0985</v>
+        <v>-0.3593</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3551</v>
+        <v>-2.9641</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.8595</v>
+        <v>-3.0885</v>
       </c>
       <c r="L13" t="n">
-        <v>1.2146</v>
+        <v>0.1244</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.4534</v>
+        <v>-1.1945</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.1403</v>
+        <v>-0.7108</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.3131</v>
+        <v>-0.4837</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.297</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q13" t="n">
         <v>-2.7793</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4823</v>
+        <v>2.0382</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6832</v>
+        <v>1.3374</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.4773</v>
+        <v>0.1884</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7941</v>
+        <v>1.149</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. ROMERO NARANJO</t>
+          <t>C. VALDES ALVAREZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.9016</v>
+        <v>-4.2589</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.5679</v>
+        <v>-2.9633</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3337</v>
+        <v>-1.2955</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.405</v>
+        <v>-3.2337</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.5756</v>
+        <v>-1.882</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8294</v>
+        <v>-1.3517</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.1995</v>
+        <v>-1.9371</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.5466</v>
+        <v>-1.2843</v>
       </c>
       <c r="L14" t="n">
         <v>-0.6529</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2056</v>
+        <v>-1.2966</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.029</v>
+        <v>-0.5977</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1766</v>
+        <v>-0.6989</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.7411</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.8529</v>
+        <v>-0.9264</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1117</v>
+        <v>0.3706</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1329</v>
+        <v>0.1601</v>
       </c>
       <c r="T14" t="n">
-        <v>0.485</v>
+        <v>-0.0998</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6479</v>
+        <v>0.2599</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.8883</v>
+        <v>-0.6294</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.0005</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.8877</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. VALDES ALVAREZ</t>
+          <t>R. ROMERO NARANJO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-4.2391</v>
+        <v>-4.6807</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.116</v>
+        <v>-4.1007</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1232</v>
+        <v>-0.5799</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.2337</v>
+        <v>-2.405</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.882</v>
+        <v>-1.5756</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.3517</v>
+        <v>-0.8294</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.9371</v>
+        <v>-2.1995</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.2843</v>
+        <v>-1.5466</v>
       </c>
       <c r="L15" t="n">
         <v>-0.6529</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.2966</v>
+        <v>-0.2056</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5977</v>
+        <v>-0.029</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6989</v>
+        <v>-0.1766</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3706</v>
+        <v>1.1117</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1798</v>
+        <v>0.3538</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2524</v>
+        <v>-0.0479</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4322</v>
+        <v>0.4016</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.6294</v>
+        <v>-1.8883</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-0.0005</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6294</v>
+        <v>-1.8877</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-10.2217</v>
+        <v>-9.401</v>
       </c>
       <c r="E16" t="n">
-        <v>-20.8446</v>
+        <v>-20.0237</v>
       </c>
       <c r="F16" t="n">
-        <v>10.6226</v>
+        <v>10.6227</v>
       </c>
       <c r="G16" t="n">
         <v>-14.4021</v>
@@ -1675,7 +1675,7 @@
         <v>-8.947099999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>-7.286700000000001</v>
+        <v>-7.2867</v>
       </c>
       <c r="K16" t="n">
         <v>-2.4088</v>
@@ -1684,7 +1684,7 @@
         <v>-4.877899999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-7.115500000000001</v>
+        <v>-7.115499999999999</v>
       </c>
       <c r="N16" t="n">
         <v>-3.0462</v>
@@ -1702,13 +1702,13 @@
         <v>15.7495</v>
       </c>
       <c r="S16" t="n">
-        <v>3.3079</v>
+        <v>4.1284</v>
       </c>
       <c r="T16" t="n">
-        <v>-2.4557</v>
+        <v>-1.6352</v>
       </c>
       <c r="U16" t="n">
-        <v>5.7637</v>
+        <v>5.7636</v>
       </c>
       <c r="V16" t="n">
         <v>-2.8332</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.8343</v>
+        <v>5.0326</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6085</v>
+        <v>1.0209</v>
       </c>
       <c r="F17" t="n">
-        <v>4.2259</v>
+        <v>4.0117</v>
       </c>
       <c r="G17" t="n">
         <v>2.6013</v>
@@ -1780,13 +1780,13 @@
         <v>2.2234</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7339</v>
+        <v>-0.0678</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.09569999999999999</v>
+        <v>-0.6833</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8296</v>
+        <v>0.6155</v>
       </c>
       <c r="V17" t="n">
         <v>1.5727</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.7761</v>
+        <v>4.1938</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0128</v>
+        <v>-0.1831</v>
       </c>
       <c r="F18" t="n">
-        <v>4.7634</v>
+        <v>4.3769</v>
       </c>
       <c r="G18" t="n">
         <v>2.9994</v>
@@ -1858,13 +1858,13 @@
         <v>1.6676</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2944</v>
+        <v>-0.2879</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7697000000000001</v>
+        <v>-0.9656</v>
       </c>
       <c r="U18" t="n">
-        <v>1.0642</v>
+        <v>0.6777</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. BRAVO ORTEGA</t>
+          <t>J. BRAVO ORTEGA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.277</v>
+        <v>1.3428</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4867</v>
+        <v>-1.6208</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7903</v>
+        <v>2.9636</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6237</v>
+        <v>2.8188</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5223</v>
+        <v>-0.1503</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1014</v>
+        <v>2.9691</v>
       </c>
       <c r="J19" t="n">
-        <v>1.198</v>
+        <v>1.7853</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0736</v>
+        <v>-0.1852</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1244</v>
+        <v>1.9705</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5743</v>
+        <v>1.0335</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5513</v>
+        <v>0.0349</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.023</v>
+        <v>0.9986</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3706</v>
+        <v>-2.7793</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1117</v>
+        <v>-4.8175</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7411</v>
+        <v>2.0382</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7083</v>
+        <v>-0.5845</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4004</v>
+        <v>-0.7909</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3079</v>
+        <v>0.2064</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3155</v>
+        <v>1.8877</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.2022</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3155</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="20">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6695</v>
+        <v>1.1924</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0453</v>
+        <v>-1.7515</v>
       </c>
       <c r="F21" t="n">
-        <v>2.7148</v>
+        <v>2.9439</v>
       </c>
       <c r="G21" t="n">
         <v>1.3873</v>
@@ -2092,13 +2092,13 @@
         <v>1.1117</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9031</v>
+        <v>-0.3802</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9302</v>
+        <v>-0.6364</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0271</v>
+        <v>0.2561</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. BRAVO ORTEGA</t>
+          <t>M. BRAVO ORTEGA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5496</v>
+        <v>0.836</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0126</v>
+        <v>0.095</v>
       </c>
       <c r="F22" t="n">
-        <v>2.5622</v>
+        <v>0.7411</v>
       </c>
       <c r="G22" t="n">
-        <v>2.8188</v>
+        <v>0.6237</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1503</v>
+        <v>0.5223</v>
       </c>
       <c r="I22" t="n">
-        <v>2.9691</v>
+        <v>0.1014</v>
       </c>
       <c r="J22" t="n">
-        <v>1.7853</v>
+        <v>1.198</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1852</v>
+        <v>1.0736</v>
       </c>
       <c r="L22" t="n">
-        <v>1.9705</v>
+        <v>0.1244</v>
       </c>
       <c r="M22" t="n">
-        <v>1.0335</v>
+        <v>-0.5743</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0349</v>
+        <v>-0.5513</v>
       </c>
       <c r="O22" t="n">
-        <v>0.9986</v>
+        <v>-0.023</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.7793</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.8175</v>
+        <v>-1.1117</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0382</v>
+        <v>0.7411</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3776</v>
+        <v>0.2674</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1826</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.195</v>
+        <v>0.2586</v>
       </c>
       <c r="V22" t="n">
-        <v>1.8877</v>
+        <v>0.3155</v>
       </c>
       <c r="W22" t="n">
-        <v>2.2022</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.3144</v>
+        <v>0.3155</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.361</v>
+        <v>0.1143</v>
       </c>
       <c r="E23" t="n">
         <v>-1.2934</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9324</v>
+        <v>1.4077</v>
       </c>
       <c r="G23" t="n">
         <v>-0.4483</v>
@@ -2248,13 +2248,13 @@
         <v>1.297</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0249</v>
+        <v>-0.5496</v>
       </c>
       <c r="T23" t="n">
         <v>-0.7113</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3136</v>
+        <v>0.1616</v>
       </c>
       <c r="V23" t="n">
         <v>0.0005</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.0396</v>
+        <v>-0.2785</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.8384</v>
+        <v>-2.4467</v>
       </c>
       <c r="F24" t="n">
-        <v>1.7988</v>
+        <v>2.1682</v>
       </c>
       <c r="G24" t="n">
         <v>-1.0881</v>
@@ -2326,13 +2326,13 @@
         <v>1.297</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0632</v>
+        <v>-0.3022</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.909</v>
+        <v>-0.5173</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1542</v>
+        <v>0.2151</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.1967</v>
+        <v>-1.345</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.7889</v>
+        <v>-3.6909</v>
       </c>
       <c r="F25" t="n">
-        <v>2.5922</v>
+        <v>2.346</v>
       </c>
       <c r="G25" t="n">
         <v>1.9706</v>
@@ -2404,13 +2404,13 @@
         <v>0.9264</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2027</v>
+        <v>-0.351</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8207</v>
+        <v>-0.7228</v>
       </c>
       <c r="U25" t="n">
-        <v>0.618</v>
+        <v>0.3718</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.5538</v>
+        <v>-1.4799</v>
       </c>
       <c r="E26" t="n">
         <v>-2.0184</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4645</v>
+        <v>0.5384</v>
       </c>
       <c r="G26" t="n">
         <v>2.2713</v>
@@ -2482,13 +2482,13 @@
         <v>0.7411</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.473</v>
+        <v>-0.3992</v>
       </c>
       <c r="T26" t="n">
         <v>-0.7449</v>
       </c>
       <c r="U26" t="n">
-        <v>0.2718</v>
+        <v>0.3457</v>
       </c>
       <c r="V26" t="n">
         <v>-0.9433</v>
@@ -2515,19 +2515,19 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>10.2216</v>
+        <v>10.8747</v>
       </c>
       <c r="E27" t="n">
-        <v>-10.6228</v>
+        <v>-10.6227</v>
       </c>
       <c r="F27" t="n">
-        <v>20.8445</v>
+        <v>21.4975</v>
       </c>
       <c r="G27" t="n">
         <v>14.4022</v>
       </c>
       <c r="H27" t="n">
-        <v>5.455</v>
+        <v>5.455000000000001</v>
       </c>
       <c r="I27" t="n">
         <v>8.9472</v>
@@ -2542,10 +2542,10 @@
         <v>4.0693</v>
       </c>
       <c r="M27" t="n">
-        <v>7.286700000000001</v>
+        <v>7.2867</v>
       </c>
       <c r="N27" t="n">
-        <v>2.4087</v>
+        <v>2.408700000000001</v>
       </c>
       <c r="O27" t="n">
         <v>4.8779</v>
@@ -2560,13 +2560,13 @@
         <v>12.0435</v>
       </c>
       <c r="S27" t="n">
-        <v>-3.3079</v>
+        <v>-2.655</v>
       </c>
       <c r="T27" t="n">
-        <v>-5.763700000000001</v>
+        <v>-5.763800000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>2.4558</v>
+        <v>3.1085</v>
       </c>
       <c r="V27" t="n">
         <v>2.8331</v>
